--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/167.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/167.xlsx
@@ -426,13 +426,13 @@
         <v>-9.833770413058238</v>
       </c>
       <c r="E2">
-        <v>-9.150544592838848</v>
+        <v>-6.188143694293115</v>
       </c>
       <c r="F2">
-        <v>-3.698933479689138</v>
+        <v>-2.887604898474298</v>
       </c>
       <c r="G2">
-        <v>-16.19435898185262</v>
+        <v>-15.65026420138233</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.219078237273687</v>
       </c>
       <c r="E3">
-        <v>-8.891674376190371</v>
+        <v>-7.766774261841009</v>
       </c>
       <c r="F3">
-        <v>-3.294141415114646</v>
+        <v>-2.494464950172652</v>
       </c>
       <c r="G3">
-        <v>-16.38983014321889</v>
+        <v>-15.05745639857442</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.479011624146535</v>
       </c>
       <c r="E4">
-        <v>-8.366262707924426</v>
+        <v>-9.0922450184641</v>
       </c>
       <c r="F4">
-        <v>-3.598770415361255</v>
+        <v>-2.851657941605653</v>
       </c>
       <c r="G4">
-        <v>-15.7378033018045</v>
+        <v>-14.91450207637038</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.714194365187263</v>
       </c>
       <c r="E5">
-        <v>-9.889691177318818</v>
+        <v>-8.431554246167018</v>
       </c>
       <c r="F5">
-        <v>-3.550991591598363</v>
+        <v>-3.155270994507508</v>
       </c>
       <c r="G5">
-        <v>-14.79855849522126</v>
+        <v>-14.7045472782698</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.932829852601325</v>
       </c>
       <c r="E6">
-        <v>-10.24706476058214</v>
+        <v>-9.811692741010704</v>
       </c>
       <c r="F6">
-        <v>-3.662786975875148</v>
+        <v>-2.887814739508094</v>
       </c>
       <c r="G6">
-        <v>-15.19946390475423</v>
+        <v>-14.46927508315765</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.181310816215522</v>
       </c>
       <c r="E7">
-        <v>-10.7880136231684</v>
+        <v>-9.407345296865818</v>
       </c>
       <c r="F7">
-        <v>-3.455422066278211</v>
+        <v>-2.716647012314441</v>
       </c>
       <c r="G7">
-        <v>-14.94325416437895</v>
+        <v>-14.30894370741798</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.49031909347113</v>
       </c>
       <c r="E8">
-        <v>-11.72837389323119</v>
+        <v>-10.41616703697657</v>
       </c>
       <c r="F8">
-        <v>-3.196234339863307</v>
+        <v>-2.583570579798937</v>
       </c>
       <c r="G8">
-        <v>-14.35382146274834</v>
+        <v>-14.34884736807558</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.904237513853309</v>
       </c>
       <c r="E9">
-        <v>-12.34649700985617</v>
+        <v>-10.38339447058306</v>
       </c>
       <c r="F9">
-        <v>-3.159814646778904</v>
+        <v>-2.516673258224859</v>
       </c>
       <c r="G9">
-        <v>-14.21729621998156</v>
+        <v>-13.7662377008014</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.461733426127329</v>
       </c>
       <c r="E10">
-        <v>-13.07307707896486</v>
+        <v>-11.56956030978219</v>
       </c>
       <c r="F10">
-        <v>-3.561095635338866</v>
+        <v>-2.608494943496123</v>
       </c>
       <c r="G10">
-        <v>-14.22962800211535</v>
+        <v>-13.43269196135598</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.20195220815965</v>
       </c>
       <c r="E11">
-        <v>-13.64023674910752</v>
+        <v>-12.9250910768682</v>
       </c>
       <c r="F11">
-        <v>-3.264173739929744</v>
+        <v>-2.521594624357087</v>
       </c>
       <c r="G11">
-        <v>-13.26130501878791</v>
+        <v>-13.54937213888759</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.150940358203558</v>
       </c>
       <c r="E12">
-        <v>-13.72109718098848</v>
+        <v>-12.5929999639897</v>
       </c>
       <c r="F12">
-        <v>-3.247368244608058</v>
+        <v>-2.215477732402924</v>
       </c>
       <c r="G12">
-        <v>-12.85103573119711</v>
+        <v>-12.02828902214082</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.3168620127639</v>
       </c>
       <c r="E13">
-        <v>-14.037850352403</v>
+        <v>-13.62235380525123</v>
       </c>
       <c r="F13">
-        <v>-2.994847920097154</v>
+        <v>-2.230915697666627</v>
       </c>
       <c r="G13">
-        <v>-12.36530255803863</v>
+        <v>-11.67098846317836</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.693009531329559</v>
       </c>
       <c r="E14">
-        <v>-15.91311860982334</v>
+        <v>-13.78863031386487</v>
       </c>
       <c r="F14">
-        <v>-2.714711723685773</v>
+        <v>-2.618980660362248</v>
       </c>
       <c r="G14">
-        <v>-11.61940354258543</v>
+        <v>-11.17420137846425</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.258861876653278</v>
       </c>
       <c r="E15">
-        <v>-15.5112799402787</v>
+        <v>-14.65134989706615</v>
       </c>
       <c r="F15">
-        <v>-2.754777899640476</v>
+        <v>-2.046458302283564</v>
       </c>
       <c r="G15">
-        <v>-11.86209963606941</v>
+        <v>-11.48816689631765</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.980219446048099</v>
       </c>
       <c r="E16">
-        <v>-16.67807749614703</v>
+        <v>-14.54187856640472</v>
       </c>
       <c r="F16">
-        <v>-1.982318212708266</v>
+        <v>-1.599656854596125</v>
       </c>
       <c r="G16">
-        <v>-11.18850955628498</v>
+        <v>-10.3193489987681</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.815435279919991</v>
       </c>
       <c r="E17">
-        <v>-18.42211510529909</v>
+        <v>-16.91638391232668</v>
       </c>
       <c r="F17">
-        <v>-1.835446909816327</v>
+        <v>-1.512955290549477</v>
       </c>
       <c r="G17">
-        <v>-11.21165026960448</v>
+        <v>-11.12487093938357</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.717136519877596</v>
       </c>
       <c r="E18">
-        <v>-17.96362975439251</v>
+        <v>-18.17141878423446</v>
       </c>
       <c r="F18">
-        <v>-1.70225724232787</v>
+        <v>-0.9645804884164564</v>
       </c>
       <c r="G18">
-        <v>-10.50114760705718</v>
+        <v>-10.06254004965022</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.633107127016201</v>
       </c>
       <c r="E19">
-        <v>-18.84959399467516</v>
+        <v>-17.96399203231312</v>
       </c>
       <c r="F19">
-        <v>-1.2562167653328</v>
+        <v>-1.169301400987568</v>
       </c>
       <c r="G19">
-        <v>-10.65133050544622</v>
+        <v>-10.1175017266932</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.506912634979241</v>
       </c>
       <c r="E20">
-        <v>-19.63123577924311</v>
+        <v>-17.78360027021757</v>
       </c>
       <c r="F20">
-        <v>-0.8991979815504966</v>
+        <v>-0.4349052938799869</v>
       </c>
       <c r="G20">
-        <v>-10.88167164297763</v>
+        <v>-10.52469882802355</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.28489430881842</v>
       </c>
       <c r="E21">
-        <v>-20.62931597900766</v>
+        <v>-19.66374569414417</v>
       </c>
       <c r="F21">
-        <v>-0.9868125520573954</v>
+        <v>-0.1032345151272498</v>
       </c>
       <c r="G21">
-        <v>-11.07007810016309</v>
+        <v>-9.958115511704985</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.92203466679753</v>
       </c>
       <c r="E22">
-        <v>-20.55294779334231</v>
+        <v>-20.64480336011389</v>
       </c>
       <c r="F22">
-        <v>-0.5930605014194319</v>
+        <v>-0.2924644082864898</v>
       </c>
       <c r="G22">
-        <v>-11.11381040673686</v>
+        <v>-9.93393197654061</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.38645495990926</v>
       </c>
       <c r="E23">
-        <v>-20.22773090400745</v>
+        <v>-20.52104922243228</v>
       </c>
       <c r="F23">
-        <v>-0.4205165337852618</v>
+        <v>0.1493594517087226</v>
       </c>
       <c r="G23">
-        <v>-11.72871444574663</v>
+        <v>-9.962273556902311</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.66133641908463</v>
       </c>
       <c r="E24">
-        <v>-21.34780819353865</v>
+        <v>-20.47821438679372</v>
       </c>
       <c r="F24">
-        <v>-0.5105145816948971</v>
+        <v>0.4688420297362378</v>
       </c>
       <c r="G24">
-        <v>-11.08013884805693</v>
+        <v>-10.79273383706511</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.74588850198229</v>
       </c>
       <c r="E25">
-        <v>-21.34403597469026</v>
+        <v>-20.7502488773825</v>
       </c>
       <c r="F25">
-        <v>-0.1479805420620759</v>
+        <v>0.1576802425884415</v>
       </c>
       <c r="G25">
-        <v>-11.6287492126428</v>
+        <v>-10.94819705558928</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.65569655020763</v>
       </c>
       <c r="E26">
-        <v>-21.59657991315002</v>
+        <v>-20.71390787347094</v>
       </c>
       <c r="F26">
-        <v>-0.2037444110506143</v>
+        <v>0.1311404988575072</v>
       </c>
       <c r="G26">
-        <v>-12.5689011087038</v>
+        <v>-11.46420185715886</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.41571915437626</v>
       </c>
       <c r="E27">
-        <v>-20.61343462066276</v>
+        <v>-21.41577153144577</v>
       </c>
       <c r="F27">
-        <v>-0.2388504200781605</v>
+        <v>0.1610574954531161</v>
       </c>
       <c r="G27">
-        <v>-11.31094677250938</v>
+        <v>-10.62834538776706</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.05861358606078</v>
       </c>
       <c r="E28">
-        <v>-20.83187462137076</v>
+        <v>-19.9370481574551</v>
       </c>
       <c r="F28">
-        <v>-0.2175234443678952</v>
+        <v>0.1105895390458072</v>
       </c>
       <c r="G28">
-        <v>-12.3948557980677</v>
+        <v>-10.7971335520868</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.61842407144682</v>
       </c>
       <c r="E29">
-        <v>-21.53807202897092</v>
+        <v>-20.11767087172504</v>
       </c>
       <c r="F29">
-        <v>-0.03075225464237484</v>
+        <v>0.3340330229492434</v>
       </c>
       <c r="G29">
-        <v>-12.00098695307845</v>
+        <v>-12.23673421147549</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.13047735455564</v>
       </c>
       <c r="E30">
-        <v>-20.896369148188</v>
+        <v>-20.56855291477274</v>
       </c>
       <c r="F30">
-        <v>0.01428359047497673</v>
+        <v>-0.1832132475628573</v>
       </c>
       <c r="G30">
-        <v>-11.97019887956323</v>
+        <v>-10.70906973019664</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.628260594562997</v>
       </c>
       <c r="E31">
-        <v>-20.30776262514501</v>
+        <v>-19.96817235930981</v>
       </c>
       <c r="F31">
-        <v>-0.1461347328176312</v>
+        <v>0.2513865378990782</v>
       </c>
       <c r="G31">
-        <v>-12.53013793098448</v>
+        <v>-11.86411244775728</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.140047928150103</v>
       </c>
       <c r="E32">
-        <v>-20.86919830414197</v>
+        <v>-19.32867484536863</v>
       </c>
       <c r="F32">
-        <v>0.05682589062846888</v>
+        <v>-0.0187865645982721</v>
       </c>
       <c r="G32">
-        <v>-12.41978420597841</v>
+        <v>-11.67602049239805</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.688122278168505</v>
       </c>
       <c r="E33">
-        <v>-20.16921396288034</v>
+        <v>-19.40023832011184</v>
       </c>
       <c r="F33">
-        <v>0.1310272638845533</v>
+        <v>-0.1613050517816257</v>
       </c>
       <c r="G33">
-        <v>-11.5181571283579</v>
+        <v>-11.13845079718566</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.285592825161137</v>
       </c>
       <c r="E34">
-        <v>-20.70093379543897</v>
+        <v>-18.63816407173104</v>
       </c>
       <c r="F34">
-        <v>-0.0292651547877772</v>
+        <v>0.5484580935172098</v>
       </c>
       <c r="G34">
-        <v>-12.14678337862795</v>
+        <v>-10.71593911219063</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.940019645810802</v>
       </c>
       <c r="E35">
-        <v>-19.27102737125098</v>
+        <v>-17.36410508051703</v>
       </c>
       <c r="F35">
-        <v>-0.1890183215959006</v>
+        <v>0.3623417661877236</v>
       </c>
       <c r="G35">
-        <v>-10.98608955983178</v>
+        <v>-10.55745998668018</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.653526661261739</v>
       </c>
       <c r="E36">
-        <v>-19.00137938646425</v>
+        <v>-18.68972074830836</v>
       </c>
       <c r="F36">
-        <v>-0.4044039098015809</v>
+        <v>0.4558548493766766</v>
       </c>
       <c r="G36">
-        <v>-10.82984836310587</v>
+        <v>-8.756331201675378</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.424213573471303</v>
       </c>
       <c r="E37">
-        <v>-18.68090833788944</v>
+        <v>-17.66669318523555</v>
       </c>
       <c r="F37">
-        <v>-0.05274201127825157</v>
+        <v>0.5394167164459659</v>
       </c>
       <c r="G37">
-        <v>-10.10735159406979</v>
+        <v>-9.497317367548289</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.247260818260992</v>
       </c>
       <c r="E38">
-        <v>-18.21254185669812</v>
+        <v>-16.79475362895466</v>
       </c>
       <c r="F38">
-        <v>-0.1895757860781353</v>
+        <v>-0.06404333669082747</v>
       </c>
       <c r="G38">
-        <v>-10.17162914626028</v>
+        <v>-9.766527620256284</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.115426442058705</v>
       </c>
       <c r="E39">
-        <v>-18.21894511894496</v>
+        <v>-16.97696130912728</v>
       </c>
       <c r="F39">
-        <v>-0.08130969043390604</v>
+        <v>0.6527340421074892</v>
       </c>
       <c r="G39">
-        <v>-9.640438872302061</v>
+        <v>-7.931253868559438</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.019894738531731</v>
       </c>
       <c r="E40">
-        <v>-18.14396264632596</v>
+        <v>-15.3978643087566</v>
       </c>
       <c r="F40">
-        <v>-0.4317038323719261</v>
+        <v>0.6708326333091312</v>
       </c>
       <c r="G40">
-        <v>-9.981302572662042</v>
+        <v>-9.244964412726265</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.951909394024607</v>
       </c>
       <c r="E41">
-        <v>-17.56011102099102</v>
+        <v>-16.68393734151296</v>
       </c>
       <c r="F41">
-        <v>-0.3421515976774871</v>
+        <v>0.4365106734725415</v>
       </c>
       <c r="G41">
-        <v>-9.527003029398935</v>
+        <v>-8.94214881224913</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.903818923508693</v>
       </c>
       <c r="E42">
-        <v>-18.42433858603686</v>
+        <v>-16.36894574648742</v>
       </c>
       <c r="F42">
-        <v>-0.4070692868572655</v>
+        <v>-0.01417322926659699</v>
       </c>
       <c r="G42">
-        <v>-9.699525489086975</v>
+        <v>-9.340000243522123</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.867918829618556</v>
       </c>
       <c r="E43">
-        <v>-16.95041086602031</v>
+        <v>-16.06835922728029</v>
       </c>
       <c r="F43">
-        <v>-0.2593134842115536</v>
+        <v>-0.02350521637332393</v>
       </c>
       <c r="G43">
-        <v>-9.34097023336513</v>
+        <v>-8.869323431476243</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.838219735232749</v>
       </c>
       <c r="E44">
-        <v>-16.96836626546072</v>
+        <v>-14.9869007640865</v>
       </c>
       <c r="F44">
-        <v>-0.4317275879606576</v>
+        <v>-0.3204936274308949</v>
       </c>
       <c r="G44">
-        <v>-9.862139485975975</v>
+        <v>-9.125907263497457</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.80976314509135</v>
       </c>
       <c r="E45">
-        <v>-16.73931152167875</v>
+        <v>-14.78298810799512</v>
       </c>
       <c r="F45">
-        <v>-0.5216789165457874</v>
+        <v>0.4311403267132863</v>
       </c>
       <c r="G45">
-        <v>-9.546568353536028</v>
+        <v>-9.301425766898536</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.782267470093263</v>
       </c>
       <c r="E46">
-        <v>-15.90751688747585</v>
+        <v>-14.04694805668441</v>
       </c>
       <c r="F46">
-        <v>-0.6010827637340904</v>
+        <v>0.09551978540744319</v>
       </c>
       <c r="G46">
-        <v>-10.69136824319816</v>
+        <v>-8.876864854214702</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.759439447037139</v>
       </c>
       <c r="E47">
-        <v>-16.55898768669331</v>
+        <v>-13.97398528347282</v>
       </c>
       <c r="F47">
-        <v>-0.4732024703271436</v>
+        <v>0.02210234657950128</v>
       </c>
       <c r="G47">
-        <v>-9.908937357719113</v>
+        <v>-9.098058954421106</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.746624815203614</v>
       </c>
       <c r="E48">
-        <v>-14.40474731650445</v>
+        <v>-13.8428452046847</v>
       </c>
       <c r="F48">
-        <v>-0.7320995867065651</v>
+        <v>-0.1008629155188792</v>
       </c>
       <c r="G48">
-        <v>-9.807810123130995</v>
+        <v>-8.45484644050503</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.749915484508417</v>
       </c>
       <c r="E49">
-        <v>-14.88359721502353</v>
+        <v>-14.44593831607822</v>
       </c>
       <c r="F49">
-        <v>-0.8574119009716268</v>
+        <v>-0.4727637837885669</v>
       </c>
       <c r="G49">
-        <v>-10.08955079070513</v>
+        <v>-10.06571486282238</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.772751790657392</v>
       </c>
       <c r="E50">
-        <v>-14.43751535442395</v>
+        <v>-13.58895178097065</v>
       </c>
       <c r="F50">
-        <v>-0.8277863062644587</v>
+        <v>-0.6460093331432767</v>
       </c>
       <c r="G50">
-        <v>-10.02085366021971</v>
+        <v>-9.639892632288083</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.817274046897606</v>
       </c>
       <c r="E51">
-        <v>-14.5128193486975</v>
+        <v>-14.92324853343469</v>
       </c>
       <c r="F51">
-        <v>-0.7271259582791274</v>
+        <v>-0.7855726250884202</v>
       </c>
       <c r="G51">
-        <v>-10.29382800320586</v>
+        <v>-9.016626155246113</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.883545726146406</v>
       </c>
       <c r="E52">
-        <v>-14.08837906538058</v>
+        <v>-13.35338962003965</v>
       </c>
       <c r="F52">
-        <v>-1.277648265633484</v>
+        <v>-0.6169229903003157</v>
       </c>
       <c r="G52">
-        <v>-9.943234609505962</v>
+        <v>-9.434989726680431</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.968547549134728</v>
       </c>
       <c r="E53">
-        <v>-14.00956550375109</v>
+        <v>-12.32130963742551</v>
       </c>
       <c r="F53">
-        <v>-1.083558770872718</v>
+        <v>-0.9856841615926448</v>
       </c>
       <c r="G53">
-        <v>-9.523338255486962</v>
+        <v>-9.668191175557773</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.066773005263102</v>
       </c>
       <c r="E54">
-        <v>-14.08199391702977</v>
+        <v>-11.99857435184686</v>
       </c>
       <c r="F54">
-        <v>-0.8924561454684709</v>
+        <v>-0.6026918089441768</v>
       </c>
       <c r="G54">
-        <v>-10.3388977701775</v>
+        <v>-9.145883095281418</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.171082023391022</v>
       </c>
       <c r="E55">
-        <v>-13.21286654310763</v>
+        <v>-11.08718273001114</v>
       </c>
       <c r="F55">
-        <v>-1.171774357774526</v>
+        <v>-0.6235151661733325</v>
       </c>
       <c r="G55">
-        <v>-9.765210023131655</v>
+        <v>-10.13379623183749</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.274274713810411</v>
       </c>
       <c r="E56">
-        <v>-13.13214649392091</v>
+        <v>-11.29356793291071</v>
       </c>
       <c r="F56">
-        <v>-1.425271828835257</v>
+        <v>-0.835809360432075</v>
       </c>
       <c r="G56">
-        <v>-10.0749645270591</v>
+        <v>-9.921858416958887</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.370397428592937</v>
       </c>
       <c r="E57">
-        <v>-12.25861744326332</v>
+        <v>-11.3178858383319</v>
       </c>
       <c r="F57">
-        <v>-1.384713120340852</v>
+        <v>-1.282176872698683</v>
       </c>
       <c r="G57">
-        <v>-9.699892959641833</v>
+        <v>-8.600099936586092</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.455811391729536</v>
       </c>
       <c r="E58">
-        <v>-12.95505146090295</v>
+        <v>-11.24402189879279</v>
       </c>
       <c r="F58">
-        <v>-1.497510198609154</v>
+        <v>-0.7503027024986261</v>
       </c>
       <c r="G58">
-        <v>-9.643050892732548</v>
+        <v>-9.685746998552528</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.527227727434163</v>
       </c>
       <c r="E59">
-        <v>-13.11836634751557</v>
+        <v>-11.48097882971815</v>
       </c>
       <c r="F59">
-        <v>-1.479802782768626</v>
+        <v>-1.095952853366947</v>
       </c>
       <c r="G59">
-        <v>-8.651386908080481</v>
+        <v>-9.31648874910222</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.582747255836304</v>
       </c>
       <c r="E60">
-        <v>-12.77173430459844</v>
+        <v>-10.57360849280124</v>
       </c>
       <c r="F60">
-        <v>-1.667316730568487</v>
+        <v>-1.295105455939373</v>
       </c>
       <c r="G60">
-        <v>-9.355387659188656</v>
+        <v>-9.135438324105017</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.621068570412815</v>
       </c>
       <c r="E61">
-        <v>-13.03355255782591</v>
+        <v>-10.46559533077029</v>
       </c>
       <c r="F61">
-        <v>-1.628033697188969</v>
+        <v>-1.201193278859729</v>
       </c>
       <c r="G61">
-        <v>-9.567080493697352</v>
+        <v>-9.572168802191213</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.643189174740338</v>
       </c>
       <c r="E62">
-        <v>-12.50742086219275</v>
+        <v>-11.22216748323178</v>
       </c>
       <c r="F62">
-        <v>-1.385647506830962</v>
+        <v>-1.220862114476529</v>
       </c>
       <c r="G62">
-        <v>-9.411226630799543</v>
+        <v>-10.0213667947783</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.653579896115598</v>
       </c>
       <c r="E63">
-        <v>-11.921318585276</v>
+        <v>-12.01275753243888</v>
       </c>
       <c r="F63">
-        <v>-1.709467855360866</v>
+        <v>-1.646148125449766</v>
       </c>
       <c r="G63">
-        <v>-9.993660839160141</v>
+        <v>-10.06989939238402</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.656750054445588</v>
       </c>
       <c r="E64">
-        <v>-11.75011509694202</v>
+        <v>-10.11479709176611</v>
       </c>
       <c r="F64">
-        <v>-1.779398765615968</v>
+        <v>-0.9358473119926385</v>
       </c>
       <c r="G64">
-        <v>-10.23321853547288</v>
+        <v>-8.832443954168761</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.65722680600427</v>
       </c>
       <c r="E65">
-        <v>-12.00739129073979</v>
+        <v>-10.10326759694258</v>
       </c>
       <c r="F65">
-        <v>-1.778905441223308</v>
+        <v>-1.808105019039223</v>
       </c>
       <c r="G65">
-        <v>-9.901905758993701</v>
+        <v>-9.622234182381609</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.65712983692386</v>
       </c>
       <c r="E66">
-        <v>-12.56125083272192</v>
+        <v>-10.48330619261429</v>
       </c>
       <c r="F66">
-        <v>-2.055315969468617</v>
+        <v>-1.604200506867521</v>
       </c>
       <c r="G66">
-        <v>-9.666482934059509</v>
+        <v>-9.130505611251504</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.658598736933525</v>
       </c>
       <c r="E67">
-        <v>-11.97005402254655</v>
+        <v>-10.78461726766265</v>
       </c>
       <c r="F67">
-        <v>-1.870855406673722</v>
+        <v>-1.146834157018186</v>
       </c>
       <c r="G67">
-        <v>-9.451373616554285</v>
+        <v>-9.500836477456536</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.66415032057254</v>
       </c>
       <c r="E68">
-        <v>-11.42452234426453</v>
+        <v>-10.31398654946749</v>
       </c>
       <c r="F68">
-        <v>-1.695733957662175</v>
+        <v>-1.080027898534246</v>
       </c>
       <c r="G68">
-        <v>-9.730720759703527</v>
+        <v>-8.58752648462794</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.676049960210719</v>
       </c>
       <c r="E69">
-        <v>-11.77503528940623</v>
+        <v>-11.02563623977289</v>
       </c>
       <c r="F69">
-        <v>-1.730457501711142</v>
+        <v>-0.847790887535332</v>
       </c>
       <c r="G69">
-        <v>-9.450539359078387</v>
+        <v>-9.202006773808682</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.695330967859833</v>
       </c>
       <c r="E70">
-        <v>-11.77564210492325</v>
+        <v>-10.76815626464477</v>
       </c>
       <c r="F70">
-        <v>-1.951877801307605</v>
+        <v>-1.475319311322016</v>
       </c>
       <c r="G70">
-        <v>-9.773493008070911</v>
+        <v>-9.173724783266689</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.720753958980509</v>
       </c>
       <c r="E71">
-        <v>-11.86575420920189</v>
+        <v>-11.38679562730662</v>
       </c>
       <c r="F71">
-        <v>-1.864538003777034</v>
+        <v>-1.412970393137081</v>
       </c>
       <c r="G71">
-        <v>-10.24195837569656</v>
+        <v>-8.748524935293776</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.750139310758116</v>
       </c>
       <c r="E72">
-        <v>-12.58756126670649</v>
+        <v>-10.94852991284429</v>
       </c>
       <c r="F72">
-        <v>-1.947485392951133</v>
+        <v>-1.245433311754573</v>
       </c>
       <c r="G72">
-        <v>-10.18668881791843</v>
+        <v>-9.544297319296088</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.781498539676147</v>
       </c>
       <c r="E73">
-        <v>-12.08572483412448</v>
+        <v>-10.96139530750008</v>
       </c>
       <c r="F73">
-        <v>-1.933757038223146</v>
+        <v>-1.195841936571459</v>
       </c>
       <c r="G73">
-        <v>-10.05493241600097</v>
+        <v>-9.343502800702673</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.814023739704038</v>
       </c>
       <c r="E74">
-        <v>-12.59093045136819</v>
+        <v>-10.64409871920464</v>
       </c>
       <c r="F74">
-        <v>-2.083822675946527</v>
+        <v>-1.225857914786783</v>
       </c>
       <c r="G74">
-        <v>-10.00032496733069</v>
+        <v>-9.871279902209903</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.846286360495721</v>
       </c>
       <c r="E75">
-        <v>-12.9094451991717</v>
+        <v>-11.72078417079434</v>
       </c>
       <c r="F75">
-        <v>-1.783723866471033</v>
+        <v>-1.599970428367382</v>
       </c>
       <c r="G75">
-        <v>-9.51988866703504</v>
+        <v>-9.484187743939541</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.876734840936336</v>
       </c>
       <c r="E76">
-        <v>-13.63221229316592</v>
+        <v>-10.1700535316077</v>
       </c>
       <c r="F76">
-        <v>-2.19990436028345</v>
+        <v>-1.772980005540691</v>
       </c>
       <c r="G76">
-        <v>-10.07662642091982</v>
+        <v>-9.777137918709649</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.903176853990464</v>
       </c>
       <c r="E77">
-        <v>-12.35039149750277</v>
+        <v>-12.76925270084224</v>
       </c>
       <c r="F77">
-        <v>-2.222621829787471</v>
+        <v>-1.324723923969922</v>
       </c>
       <c r="G77">
-        <v>-10.10490510091627</v>
+        <v>-8.994720275412757</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.924223721397552</v>
       </c>
       <c r="E78">
-        <v>-14.10512083378694</v>
+        <v>-11.64555263210491</v>
       </c>
       <c r="F78">
-        <v>-2.238562621679327</v>
+        <v>-1.739861547437022</v>
       </c>
       <c r="G78">
-        <v>-10.41288184188913</v>
+        <v>-10.01314339965875</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.940662702748393</v>
       </c>
       <c r="E79">
-        <v>-13.57074731545982</v>
+        <v>-12.62185087189257</v>
       </c>
       <c r="F79">
-        <v>-2.399688069663178</v>
+        <v>-1.485595187154345</v>
       </c>
       <c r="G79">
-        <v>-10.06377819368191</v>
+        <v>-8.525039937574196</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.951809816163244</v>
       </c>
       <c r="E80">
-        <v>-14.6826144816151</v>
+        <v>-12.8255552181796</v>
       </c>
       <c r="F80">
-        <v>-2.534843116192696</v>
+        <v>-1.391864344402019</v>
       </c>
       <c r="G80">
-        <v>-10.59197904501816</v>
+        <v>-8.659395117739978</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.956850649777834</v>
       </c>
       <c r="E81">
-        <v>-14.438135755363</v>
+        <v>-14.25943764254632</v>
       </c>
       <c r="F81">
-        <v>-2.561306842039689</v>
+        <v>-2.209892793492126</v>
       </c>
       <c r="G81">
-        <v>-10.65123118908004</v>
+        <v>-9.590913111034565</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.952839097306421</v>
       </c>
       <c r="E82">
-        <v>-14.97914348811137</v>
+        <v>-14.53313408309591</v>
       </c>
       <c r="F82">
-        <v>-2.485202646126204</v>
+        <v>-2.049594039996134</v>
       </c>
       <c r="G82">
-        <v>-10.25556140731742</v>
+        <v>-8.918379095277162</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.937436910713592</v>
       </c>
       <c r="E83">
-        <v>-16.85065764057935</v>
+        <v>-14.52925318087134</v>
       </c>
       <c r="F83">
-        <v>-2.603506269862489</v>
+        <v>-2.236229031012927</v>
       </c>
       <c r="G83">
-        <v>-9.846046924109578</v>
+        <v>-8.603076117025896</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.908423886152769</v>
       </c>
       <c r="E84">
-        <v>-16.97736887178797</v>
+        <v>-15.86589115439734</v>
       </c>
       <c r="F84">
-        <v>-2.662525446360213</v>
+        <v>-2.023691737896164</v>
       </c>
       <c r="G84">
-        <v>-9.996785994149212</v>
+        <v>-9.449235004135916</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.862967895529219</v>
       </c>
       <c r="E85">
-        <v>-17.70829627594402</v>
+        <v>-16.21304850029936</v>
       </c>
       <c r="F85">
-        <v>-2.677672801588434</v>
+        <v>-2.136113477862506</v>
       </c>
       <c r="G85">
-        <v>-9.835141987103219</v>
+        <v>-9.933908802721835</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.798312907941848</v>
       </c>
       <c r="E86">
-        <v>-19.44451773895884</v>
+        <v>-17.37110157285888</v>
       </c>
       <c r="F86">
-        <v>-3.07459780702798</v>
+        <v>-2.072752571597605</v>
       </c>
       <c r="G86">
-        <v>-9.681979597728837</v>
+        <v>-9.396097437685073</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.711532305401803</v>
       </c>
       <c r="E87">
-        <v>-20.45409573422887</v>
+        <v>-18.81037740976873</v>
       </c>
       <c r="F87">
-        <v>-2.972528752630865</v>
+        <v>-2.605964181443251</v>
       </c>
       <c r="G87">
-        <v>-10.19182347404984</v>
+        <v>-9.77086112436719</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.601565019937048</v>
       </c>
       <c r="E88">
-        <v>-21.6798721355731</v>
+        <v>-19.13686227182573</v>
       </c>
       <c r="F88">
-        <v>-2.867418191023149</v>
+        <v>-2.29592920105429</v>
       </c>
       <c r="G88">
-        <v>-10.27059790515679</v>
+        <v>-8.404410279214233</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.469732224484662</v>
       </c>
       <c r="E89">
-        <v>-22.13670912194089</v>
+        <v>-21.9408797919532</v>
       </c>
       <c r="F89">
-        <v>-2.998181621049154</v>
+        <v>-2.617613922157223</v>
       </c>
       <c r="G89">
-        <v>-10.18783426667501</v>
+        <v>-9.165176954684291</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.319220470451837</v>
       </c>
       <c r="E90">
-        <v>-23.92200112930283</v>
+        <v>-22.35941947363812</v>
       </c>
       <c r="F90">
-        <v>-3.108805854801472</v>
+        <v>-2.944967518584473</v>
       </c>
       <c r="G90">
-        <v>-9.701614443322255</v>
+        <v>-8.812411843110631</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.154183499224266</v>
       </c>
       <c r="E91">
-        <v>-25.80220995186554</v>
+        <v>-24.44781130328145</v>
       </c>
       <c r="F91">
-        <v>-3.317152662065982</v>
+        <v>-2.36473884752126</v>
       </c>
       <c r="G91">
-        <v>-10.69386439453477</v>
+        <v>-9.554718916653714</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.97904236868753</v>
       </c>
       <c r="E92">
-        <v>-27.63494678140584</v>
+        <v>-26.09255306286733</v>
       </c>
       <c r="F92">
-        <v>-2.898446949171396</v>
+        <v>-2.858687220311332</v>
       </c>
       <c r="G92">
-        <v>-10.35796982302924</v>
+        <v>-10.15437789345514</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.798417238544837</v>
       </c>
       <c r="E93">
-        <v>-29.709658091072</v>
+        <v>-29.18355356628288</v>
       </c>
       <c r="F93">
-        <v>-3.079142251152334</v>
+        <v>-2.650670615730191</v>
       </c>
       <c r="G93">
-        <v>-11.11368460600637</v>
+        <v>-9.368798679168243</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.619830004127202</v>
       </c>
       <c r="E94">
-        <v>-31.95741371375626</v>
+        <v>-30.71363209975754</v>
       </c>
       <c r="F94">
-        <v>-2.77483078394177</v>
+        <v>-2.195832652374855</v>
       </c>
       <c r="G94">
-        <v>-10.05166490755371</v>
+        <v>-10.18382519602696</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.452141320077917</v>
       </c>
       <c r="E95">
-        <v>-33.26819862917248</v>
+        <v>-32.45688175443227</v>
       </c>
       <c r="F95">
-        <v>-3.192469870902307</v>
+        <v>-2.740373302486597</v>
       </c>
       <c r="G95">
-        <v>-10.75753942743711</v>
+        <v>-9.745909542637703</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.312572298014439</v>
       </c>
       <c r="E96">
-        <v>-36.29753037355158</v>
+        <v>-35.61381910363651</v>
       </c>
       <c r="F96">
-        <v>-2.635771902330694</v>
+        <v>-2.565075270265477</v>
       </c>
       <c r="G96">
-        <v>-11.19193928146366</v>
+        <v>-9.871783105131872</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.210905483672325</v>
       </c>
       <c r="E97">
-        <v>-38.99967307816549</v>
+        <v>-39.61293261370623</v>
       </c>
       <c r="F97">
-        <v>-2.955250521093421</v>
+        <v>-2.166791445150484</v>
       </c>
       <c r="G97">
-        <v>-11.408154321179</v>
+        <v>-10.66200039371929</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.180955608439795</v>
       </c>
       <c r="E98">
-        <v>-41.98587790033254</v>
+        <v>-40.63531486923295</v>
       </c>
       <c r="F98">
-        <v>-2.86343121138103</v>
+        <v>-2.441449602800359</v>
       </c>
       <c r="G98">
-        <v>-11.22195268732269</v>
+        <v>-10.37791254935781</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.22609138239909</v>
       </c>
       <c r="E99">
-        <v>-43.6126053903159</v>
+        <v>-42.72950993831711</v>
       </c>
       <c r="F99">
-        <v>-2.717624158864267</v>
+        <v>-2.061786991839102</v>
       </c>
       <c r="G99">
-        <v>-12.11018198714577</v>
+        <v>-10.63981973860617</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.400278579384099</v>
       </c>
       <c r="E100">
-        <v>-47.02791255979077</v>
+        <v>-47.5462303735237</v>
       </c>
       <c r="F100">
-        <v>-2.776004310025111</v>
+        <v>-1.86515089796631</v>
       </c>
       <c r="G100">
-        <v>-12.26910803630402</v>
+        <v>-10.74265852523809</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.665245285757598</v>
       </c>
       <c r="E101">
-        <v>-48.83740020377569</v>
+        <v>-48.93885953179905</v>
       </c>
       <c r="F101">
-        <v>-2.926920397825082</v>
+        <v>-2.107054058020108</v>
       </c>
       <c r="G101">
-        <v>-13.31708440057909</v>
+        <v>-11.07433546172659</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.113807615995388</v>
       </c>
       <c r="E102">
-        <v>-51.5521784829895</v>
+        <v>-50.79192694539678</v>
       </c>
       <c r="F102">
-        <v>-2.302097735594926</v>
+        <v>-1.851151729526783</v>
       </c>
       <c r="G102">
-        <v>-13.17910417304781</v>
+        <v>-11.33736161536723</v>
       </c>
     </row>
   </sheetData>
